--- a/data/file_generation/reference/data_126/开发类型统计_W45_W46_res.xlsx
+++ b/data/file_generation/reference/data_126/开发类型统计_W45_W46_res.xlsx
@@ -1514,18 +1514,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{676ACEB2-5CF6-4B62-937A-1BDC62216830}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E845E24-AA47-44A7-9A50-2482FEF9E47A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DF11A09-9220-4BCD-A19D-0A0755BF07E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{041CF3B3-C23F-4B65-8A9C-BCDDACBF9621}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92542C51-E2CB-4B8E-84ED-77679E3277BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A9759A-A23C-4608-8F09-F4732C392C23}"/>
 </file>